--- a/database/seeders/excel/team.xlsx
+++ b/database/seeders/excel/team.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\database\seeders\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C520F646-CC1E-48EE-8E0E-3A0C21117767}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FF8641-CF8E-4218-96DF-5E81A8228960}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
@@ -33,9 +33,6 @@
     <t>fungsi</t>
   </si>
   <si>
-    <t>Kepala Kantor</t>
-  </si>
-  <si>
     <t>Kepala Bagian Umum</t>
   </si>
   <si>
@@ -61,6 +58,18 @@
   </si>
   <si>
     <t>Tidak Diketahui</t>
+  </si>
+  <si>
+    <t>Kepala BPS Provinsi</t>
+  </si>
+  <si>
+    <t>Kepala BPS Kabupaten/Kota</t>
+  </si>
+  <si>
+    <t>Kepala Sub Bagian Umum</t>
+  </si>
+  <si>
+    <t>Staf BPS Kabupaten/Kota</t>
   </si>
 </sst>
 </file>
@@ -378,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -394,7 +403,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -402,7 +411,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -410,7 +419,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -418,7 +427,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -426,7 +435,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -434,7 +443,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -442,7 +451,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -450,7 +459,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -458,15 +467,39 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>99</v>
       </c>
-      <c r="B11" t="s">
-        <v>11</v>
+      <c r="B14" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
